--- a/缓存数据/infoPlow_count_8_Part.xlsx
+++ b/缓存数据/infoPlow_count_8_Part.xlsx
@@ -485,16 +485,16 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -503,7 +503,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>8</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
         <v>8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
         <v>55</v>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
@@ -584,13 +584,13 @@
         <v>9</v>
       </c>
       <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
         <v>9</v>
       </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="D9" t="n">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="E9" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F9" t="n">
         <v>379</v>
       </c>
       <c r="G9" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="H9" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="I9" t="n">
-        <v>410</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
@@ -739,13 +739,13 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -767,10 +767,10 @@
         <v>24</v>
       </c>
       <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="n">
         <v>24</v>
-      </c>
-      <c r="E11" t="n">
-        <v>23</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
@@ -779,7 +779,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" t="n">
         <v>23</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
@@ -810,7 +810,7 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
         <v>15</v>

--- a/缓存数据/infoPlow_count_8_Part.xlsx
+++ b/缓存数据/infoPlow_count_8_Part.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -547,13 +547,13 @@
         <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
         <v>54</v>
@@ -565,7 +565,7 @@
         <v>55</v>
       </c>
       <c r="I4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="C9" t="n">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="E9" t="n">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="F9" t="n">
-        <v>379</v>
+        <v>280</v>
       </c>
       <c r="G9" t="n">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="H9" t="n">
-        <v>410</v>
+        <v>272</v>
       </c>
       <c r="I9" t="n">
-        <v>382</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -730,28 +730,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -792,31 +792,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>